--- a/examples/03_Nb2O5_on_BK7_60deg.xlsx
+++ b/examples/03_Nb2O5_on_BK7_60deg.xlsx
@@ -3731,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3879,10 +3879,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Возможные дефекты</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/03_Nb2O5_on_BK7_60deg.xlsx
+++ b/examples/03_Nb2O5_on_BK7_60deg.xlsx
@@ -3731,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3801,100 +3801,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>60</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±5</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>420 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/03_Nb2O5_on_BK7_60deg.xlsx
+++ b/examples/03_Nb2O5_on_BK7_60deg.xlsx
@@ -478,16 +478,16 @@
         <v>420</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>10.5925</v>
+        <v>10.78</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>104.2194</v>
+        <v>105.4889</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1937</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>422</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14.6031</v>
+        <v>14.6976</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>128.9207</v>
+        <v>129.4605</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0316</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1422</v>
+        <v>0.1414</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +512,16 @@
         <v>424</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17.1561</v>
+        <v>17.1967</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>144.3718</v>
+        <v>144.6099</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0313</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1221</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="5">
@@ -529,16 +529,16 @@
         <v>426</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>18.9747</v>
+        <v>18.9916</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>156.4496</v>
+        <v>156.5649</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1115</v>
+        <v>0.1114</v>
       </c>
     </row>
     <row r="6">
@@ -546,10 +546,10 @@
         <v>428</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>19.971</v>
+        <v>19.9776</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>167.3296</v>
+        <v>167.3809</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0308</v>
@@ -563,10 +563,10 @@
         <v>430</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>20.2868</v>
+        <v>20.29</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>177.7017</v>
+        <v>177.7096</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0305</v>
@@ -580,10 +580,10 @@
         <v>432</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>20.1634</v>
+        <v>20.1678</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>187.7383</v>
+        <v>187.7079</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0302</v>
@@ -597,10 +597,10 @@
         <v>434</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>19.3078</v>
+        <v>19.3181</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>198.2891</v>
+        <v>198.2146</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0299</v>
@@ -614,16 +614,16 @@
         <v>436</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>18.0132</v>
+        <v>18.0357</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>208.9135</v>
+        <v>208.7736</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0297</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1109</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="11">
@@ -631,16 +631,16 @@
         <v>438</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16.1085</v>
+        <v>16.1542</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>220.7808</v>
+        <v>220.5181</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.121</v>
+        <v>0.1207</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         <v>440</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>13.5978</v>
+        <v>13.6872</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>236.4705</v>
+        <v>235.9384</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1406</v>
+        <v>0.1398</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>442</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>9.7903</v>
+        <v>9.9269</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>262.1605</v>
+        <v>261.1183</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1895</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="14">
@@ -682,16 +682,16 @@
         <v>444</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5.4233</v>
+        <v>5.416</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>324.6562</v>
+        <v>323.6622</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.3372</v>
+        <v>0.3376</v>
       </c>
     </row>
     <row r="15">
@@ -699,16 +699,16 @@
         <v>446</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>7.154</v>
+        <v>7.2473</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>73.49979999999999</v>
+        <v>74.77589999999999</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0283</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.2505</v>
+        <v>0.2474</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>448</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11.545</v>
+        <v>11.6554</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>110.7572</v>
+        <v>111.4898</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0281</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1579</v>
+        <v>0.1565</v>
       </c>
     </row>
     <row r="17">
@@ -733,16 +733,16 @@
         <v>450</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>14.485</v>
+        <v>14.5437</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>129.49</v>
+        <v>129.8432</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0278</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.1264</v>
+        <v>0.1259</v>
       </c>
     </row>
     <row r="18">
@@ -750,16 +750,16 @@
         <v>452</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>16.5471</v>
+        <v>16.5764</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>142.8245</v>
+        <v>143.003</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0275</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.1111</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         <v>454</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>18.0245</v>
+        <v>18.0389</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>153.291</v>
+        <v>153.3885</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0273</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.1022</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="20">
@@ -784,16 +784,16 @@
         <v>456</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>19.0171</v>
+        <v>19.0238</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>162.4886</v>
+        <v>162.5414</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -801,10 +801,10 @@
         <v>458</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>19.5434</v>
+        <v>19.5465</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>171.3509</v>
+        <v>171.3743</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0268</v>
@@ -818,10 +818,10 @@
         <v>460</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>19.7671</v>
+        <v>19.7691</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>179.9131</v>
+        <v>179.9132</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0266</v>
@@ -835,10 +835,10 @@
         <v>462</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>19.5007</v>
+        <v>19.5037</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>188.4671</v>
+        <v>188.4452</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0263</v>
@@ -852,10 +852,10 @@
         <v>464</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>18.9052</v>
+        <v>18.9112</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>197.0557</v>
+        <v>197.009</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0261</v>
@@ -869,10 +869,10 @@
         <v>466</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>17.9769</v>
+        <v>17.9886</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>205.8297</v>
+        <v>205.7498</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0258</v>
@@ -886,16 +886,16 @@
         <v>468</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>16.6547</v>
+        <v>16.6761</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>215.1523</v>
+        <v>215.0199</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0256</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.1026</v>
+        <v>0.1025</v>
       </c>
     </row>
     <row r="27">
@@ -903,16 +903,16 @@
         <v>470</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>14.9251</v>
+        <v>14.9628</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>226.1118</v>
+        <v>225.8837</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0254</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.112</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="28">
@@ -920,16 +920,16 @@
         <v>472</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>12.6469</v>
+        <v>12.7112</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>240.3819</v>
+        <v>239.9709</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0251</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.1291</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="29">
@@ -937,16 +937,16 @@
         <v>474</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>9.624599999999999</v>
+        <v>9.712999999999999</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>262.5742</v>
+        <v>261.8666</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0249</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.1652</v>
       </c>
     </row>
     <row r="30">
@@ -954,16 +954,16 @@
         <v>476</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5.8842</v>
+        <v>5.906</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>307.8524</v>
+        <v>307.0125</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.0247</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.2668</v>
+        <v>0.2658</v>
       </c>
     </row>
     <row r="31">
@@ -971,16 +971,16 @@
         <v>478</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>5.5011</v>
+        <v>5.5079</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42.6552</v>
+        <v>43.4313</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.2827</v>
+        <v>0.2823</v>
       </c>
     </row>
     <row r="32">
@@ -988,16 +988,16 @@
         <v>480</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9.0282</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>92.59010000000001</v>
+        <v>93.30410000000001</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.1721</v>
+        <v>0.1706</v>
       </c>
     </row>
     <row r="33">
@@ -1005,16 +1005,16 @@
         <v>482</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>12.1011</v>
+        <v>12.1627</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>115.8243</v>
+        <v>116.2367</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.024</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.1291</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="34">
@@ -1022,16 +1022,16 @@
         <v>484</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>14.2938</v>
+        <v>14.3296</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>130.3497</v>
+        <v>130.5755</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0238</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.1096</v>
+        <v>0.1093</v>
       </c>
     </row>
     <row r="35">
@@ -1039,16 +1039,16 @@
         <v>486</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>15.915</v>
+        <v>15.9353</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>141.0765</v>
+        <v>141.206</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0236</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0985</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="36">
@@ -1056,10 +1056,10 @@
         <v>488</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>17.1405</v>
+        <v>17.1519</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>149.924</v>
+        <v>150.0023</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0234</v>
@@ -1073,10 +1073,10 @@
         <v>490</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>18.0993</v>
+        <v>18.1056</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>158.1549</v>
+        <v>158.2029</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0232</v>
@@ -1090,16 +1090,16 @@
         <v>492</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>18.7589</v>
+        <v>18.7622</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>165.3972</v>
+        <v>165.4251</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.0832</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1107,10 +1107,10 @@
         <v>494</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>19.0876</v>
+        <v>19.0893</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>172.6532</v>
+        <v>172.6661</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0228</v>
@@ -1124,10 +1124,10 @@
         <v>496</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>19.1852</v>
+        <v>19.1865</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>179.726</v>
+        <v>179.7262</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0226</v>
@@ -1141,10 +1141,10 @@
         <v>498</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>19.0424</v>
+        <v>19.0441</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>186.7774</v>
+        <v>186.7656</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0224</v>
@@ -1158,10 +1158,10 @@
         <v>500</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>18.6795</v>
+        <v>18.6825</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>193.9902</v>
+        <v>193.9655</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0222</v>
@@ -1175,16 +1175,16 @@
         <v>502</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>18.1038</v>
+        <v>18.1091</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>201.0259</v>
+        <v>200.9857</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.022</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.0822</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1192,16 +1192,16 @@
         <v>504</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>17.1873</v>
+        <v>17.1961</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>208.4307</v>
+        <v>208.3698</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0218</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0849</v>
       </c>
     </row>
     <row r="45">
@@ -1209,16 +1209,16 @@
         <v>506</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16.1498</v>
+        <v>16.1641</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>216.3881</v>
+        <v>216.2959</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0216</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.0893</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="46">
@@ -1226,16 +1226,16 @@
         <v>508</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>14.8233</v>
+        <v>14.8458</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>225.4426</v>
+        <v>225.2995</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0215</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         <v>510</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>13.0849</v>
+        <v>13.1198</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>236.21</v>
+        <v>235.9813</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0213</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.106</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>512</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>10.9729</v>
+        <v>11.0233</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>251.5678</v>
+        <v>251.1996</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.0211</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.1241</v>
+        <v>0.1236</v>
       </c>
     </row>
     <row r="49">
@@ -1277,16 +1277,16 @@
         <v>514</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>8.249000000000001</v>
+        <v>8.3009</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>274.496</v>
+        <v>273.9629</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0209</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.1623</v>
+        <v>0.1613</v>
       </c>
     </row>
     <row r="50">
@@ -1294,10 +1294,10 @@
         <v>516</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>5.3951</v>
+        <v>5.3966</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>319.4487</v>
+        <v>318.9692</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0207</v>
@@ -1311,16 +1311,16 @@
         <v>518</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5.2502</v>
+        <v>5.2475</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>35.9335</v>
+        <v>36.3822</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0206</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.2492</v>
+        <v>0.2493</v>
       </c>
     </row>
     <row r="52">
@@ -1328,16 +1328,16 @@
         <v>520</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>7.9356</v>
+        <v>7.9827</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>82.1063</v>
+        <v>82.62860000000001</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.1645</v>
+        <v>0.1636</v>
       </c>
     </row>
     <row r="53">
@@ -1345,16 +1345,16 @@
         <v>522</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>10.5837</v>
+        <v>10.6303</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>105.7541</v>
+        <v>106.1093</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.0202</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.1233</v>
+        <v>0.1228</v>
       </c>
     </row>
     <row r="54">
@@ -1362,16 +1362,16 @@
         <v>524</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>12.6332</v>
+        <v>12.6654</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>120.8935</v>
+        <v>121.1127</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0201</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1034</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="55">
@@ -1379,16 +1379,16 @@
         <v>526</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>14.2071</v>
+        <v>14.2277</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>131.7671</v>
+        <v>131.9027</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0199</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.092</v>
+        <v>0.0919</v>
       </c>
     </row>
     <row r="56">
@@ -1396,10 +1396,10 @@
         <v>528</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>15.4909</v>
+        <v>15.504</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>140.3301</v>
+        <v>140.417</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0198</v>
@@ -1413,16 +1413,16 @@
         <v>530</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>16.5095</v>
+        <v>16.5177</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>147.8315</v>
+        <v>147.8891</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0196</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.0793</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1430,10 +1430,10 @@
         <v>532</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>17.3065</v>
+        <v>17.3116</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>154.5828</v>
+        <v>154.6216</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0195</v>
@@ -1447,10 +1447,10 @@
         <v>534</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>17.9271</v>
+        <v>17.9302</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>160.7635</v>
+        <v>160.7894</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0193</v>
@@ -1464,10 +1464,10 @@
         <v>536</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>18.3666</v>
+        <v>18.3684</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>166.9092</v>
+        <v>166.9254</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0192</v>
@@ -1481,10 +1481,10 @@
         <v>538</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>18.6444</v>
+        <v>18.6455</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>172.621</v>
+        <v>172.6294</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.019</v>
@@ -1498,10 +1498,10 @@
         <v>540</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>18.7212</v>
+        <v>18.722</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>178.4893</v>
+        <v>178.491</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0189</v>
@@ -1515,10 +1515,10 @@
         <v>542</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>18.6872</v>
+        <v>18.6881</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>184.2161</v>
+        <v>184.2115</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0187</v>
@@ -1532,10 +1532,10 @@
         <v>544</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>18.4425</v>
+        <v>18.4438</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>189.9729</v>
+        <v>189.9618</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0186</v>
@@ -1549,10 +1549,10 @@
         <v>546</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>18.0579</v>
+        <v>18.0601</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>195.6541</v>
+        <v>195.6359</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0185</v>
@@ -1566,10 +1566,10 @@
         <v>548</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>17.5904</v>
+        <v>17.5937</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>201.3996</v>
+        <v>201.3732</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0183</v>
@@ -1583,16 +1583,16 @@
         <v>550</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>16.9553</v>
+        <v>16.9604</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>207.3549</v>
+        <v>207.3179</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0182</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="68">
@@ -1600,16 +1600,16 @@
         <v>552</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>16.1235</v>
+        <v>16.1309</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>213.7254</v>
+        <v>213.6741</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0181</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.0745</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1617,16 +1617,16 @@
         <v>554</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>15.2055</v>
+        <v>15.2162</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>220.6542</v>
+        <v>220.5823</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0179</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="70">
@@ -1634,16 +1634,16 @@
         <v>556</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>14.0718</v>
+        <v>14.0872</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>228.2225</v>
+        <v>228.1198</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0178</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="71">
@@ -1651,16 +1651,16 @@
         <v>558</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>12.7829</v>
+        <v>12.8046</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>237.5667</v>
+        <v>237.4168</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.0177</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.0905</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1668,16 +1668,16 @@
         <v>560</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>11.1416</v>
+        <v>11.1708</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>249.1573</v>
+        <v>248.9396</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0176</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.1022</v>
+        <v>0.1019</v>
       </c>
     </row>
     <row r="73">
@@ -1685,16 +1685,16 @@
         <v>562</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>9.1287</v>
+        <v>9.1622</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>265.5598</v>
+        <v>265.2573</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0175</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.1225</v>
+        <v>0.1221</v>
       </c>
     </row>
     <row r="74">
@@ -1702,16 +1702,16 @@
         <v>564</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6.8879</v>
+        <v>6.9103</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>290.9759</v>
+        <v>290.6124</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0174</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.1613</v>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="75">
@@ -1719,16 +1719,16 @@
         <v>566</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>4.9645</v>
+        <v>4.9567</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>335.5742</v>
+        <v>335.3731</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0173</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.22</v>
+        <v>0.2203</v>
       </c>
     </row>
     <row r="76">
@@ -1736,16 +1736,16 @@
         <v>568</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>5.2119</v>
+        <v>5.2098</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>34.9789</v>
+        <v>35.2537</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0172</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.2089</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="77">
@@ -1753,16 +1753,16 @@
         <v>570</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>7.1886</v>
+        <v>7.2135</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>74.0044</v>
+        <v>74.3492</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.017</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.1505</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78">
@@ -1770,16 +1770,16 @@
         <v>572</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>9.372199999999999</v>
+        <v>9.4026</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>96.5767</v>
+        <v>96.8451</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0169</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.1159</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="79">
@@ -1787,16 +1787,16 @@
         <v>574</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>11.1645</v>
+        <v>11.1894</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>111.5812</v>
+        <v>111.7687</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0168</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="80">
@@ -1804,16 +1804,16 @@
         <v>576</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>12.6879</v>
+        <v>12.706</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>122.424</v>
+        <v>122.5514</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0168</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.0861</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -1821,16 +1821,16 @@
         <v>578</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13.8595</v>
+        <v>13.8722</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>130.9538</v>
+        <v>131.0411</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0167</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0788</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -1838,10 +1838,10 @@
         <v>580</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>14.8723</v>
+        <v>14.8811</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>138.0945</v>
+        <v>138.1556</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0166</v>
@@ -1855,10 +1855,10 @@
         <v>582</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>15.671</v>
+        <v>15.6771</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>144.3633</v>
+        <v>144.4071</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0165</v>
@@ -1872,10 +1872,10 @@
         <v>584</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16.4035</v>
+        <v>16.4077</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>150.1021</v>
+        <v>150.1339</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0164</v>
@@ -1889,10 +1889,10 @@
         <v>586</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>16.992</v>
+        <v>16.9949</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>155.2046</v>
+        <v>155.2279</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0163</v>
@@ -1906,10 +1906,10 @@
         <v>588</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>17.4565</v>
+        <v>17.4584</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>160.2518</v>
+        <v>160.2687</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0162</v>
@@ -1923,10 +1923,10 @@
         <v>590</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>17.7825</v>
+        <v>17.7838</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>165.1641</v>
+        <v>165.1759</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.0162</v>
@@ -1940,10 +1940,10 @@
         <v>592</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>18.0737</v>
+        <v>18.0745</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>169.8609</v>
+        <v>169.8685</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0161</v>
@@ -1957,10 +1957,10 @@
         <v>594</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>18.2325</v>
+        <v>18.2331</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>174.6213</v>
+        <v>174.6252</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.016</v>
@@ -1974,10 +1974,10 @@
         <v>596</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>18.2769</v>
+        <v>18.2774</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>179.0418</v>
+        <v>179.0425</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0159</v>
@@ -1991,10 +1991,10 @@
         <v>598</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>18.2441</v>
+        <v>18.2446</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>183.5941</v>
+        <v>183.5916</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0159</v>
@@ -2008,10 +2008,10 @@
         <v>600</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>18.1176</v>
+        <v>18.1183</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>188.0344</v>
+        <v>188.0288</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0158</v>
@@ -2025,10 +2025,10 @@
         <v>602</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>17.9035</v>
+        <v>17.9045</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>192.6943</v>
+        <v>192.6854</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0157</v>
@@ -2042,10 +2042,10 @@
         <v>604</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>17.5272</v>
+        <v>17.5286</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>197.1702</v>
+        <v>197.1577</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0157</v>
@@ -2059,10 +2059,10 @@
         <v>606</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>17.1703</v>
+        <v>17.1724</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>201.8422</v>
+        <v>201.8255</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0156</v>
@@ -2076,10 +2076,10 @@
         <v>608</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>16.6949</v>
+        <v>16.6977</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>206.7033</v>
+        <v>206.6815</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0156</v>
@@ -2093,10 +2093,10 @@
         <v>610</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>16.0993</v>
+        <v>16.1031</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>211.5087</v>
+        <v>211.4806</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0155</v>
@@ -2110,10 +2110,10 @@
         <v>612</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>15.4421</v>
+        <v>15.4473</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>216.6913</v>
+        <v>216.655</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0155</v>
@@ -2127,10 +2127,10 @@
         <v>614</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>14.6623</v>
+        <v>14.6691</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>222.2483</v>
+        <v>222.201</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.0154</v>
@@ -2144,10 +2144,10 @@
         <v>616</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13.8438</v>
+        <v>13.8527</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>228.5679</v>
+        <v>228.5053</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0154</v>
@@ -2161,16 +2161,16 @@
         <v>618</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>12.847</v>
+        <v>12.8587</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>235.5114</v>
+        <v>235.4278</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.0779</v>
+        <v>0.07779999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -2178,16 +2178,16 @@
         <v>620</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>11.6973</v>
+        <v>11.7123</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>244.0451</v>
+        <v>243.9329</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.0847</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -2195,16 +2195,16 @@
         <v>622</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>10.3804</v>
+        <v>10.3986</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>254.6519</v>
+        <v>254.5033</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.0948</v>
+        <v>0.09470000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -2212,16 +2212,16 @@
         <v>624</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>8.822699999999999</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>268.5255</v>
+        <v>268.3368</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0152</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.1107</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="105">
@@ -2229,16 +2229,16 @@
         <v>626</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7.0772</v>
+        <v>7.0917</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>287.6204</v>
+        <v>287.4041</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0152</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.1367</v>
+        <v>0.1364</v>
       </c>
     </row>
     <row r="106">
@@ -2246,10 +2246,10 @@
         <v>628</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5.4569</v>
+        <v>5.4584</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>317.337</v>
+        <v>317.1528</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0152</v>
@@ -2263,16 +2263,16 @@
         <v>630</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>4.7593</v>
+        <v>4.7516</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>0.4215</v>
+        <v>0.4287</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.2018</v>
+        <v>0.2021</v>
       </c>
     </row>
     <row r="108">
@@ -2280,16 +2280,16 @@
         <v>632</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5.4886</v>
+        <v>5.4906</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>43.0813</v>
+        <v>43.2676</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.1745</v>
+        <v>0.1744</v>
       </c>
     </row>
     <row r="109">
@@ -2297,16 +2297,16 @@
         <v>634</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>7.0624</v>
+        <v>7.0762</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>71.70650000000001</v>
+        <v>71.914</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.1361</v>
+        <v>0.1359</v>
       </c>
     </row>
     <row r="110">
@@ -2314,16 +2314,16 @@
         <v>636</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>8.7455</v>
+        <v>8.763</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>90.79049999999999</v>
+        <v>90.9654</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.1107</v>
+        <v>0.1105</v>
       </c>
     </row>
     <row r="111">
@@ -2331,16 +2331,16 @@
         <v>638</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>10.1996</v>
+        <v>10.2158</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>104.0475</v>
+        <v>104.1833</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.0951</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="112">
@@ -2348,16 +2348,16 @@
         <v>640</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>11.4249</v>
+        <v>11.4381</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>114.285</v>
+        <v>114.3865</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.0851</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -2365,10 +2365,10 @@
         <v>642</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>12.5002</v>
+        <v>12.5104</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>122.3892</v>
+        <v>122.4644</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.015</v>
@@ -2382,10 +2382,10 @@
         <v>644</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13.3819</v>
+        <v>13.3897</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>129.1001</v>
+        <v>129.1562</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.015</v>
@@ -2399,16 +2399,16 @@
         <v>646</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>14.1753</v>
+        <v>14.1811</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>135.108</v>
+        <v>135.1502</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="116">
@@ -2416,10 +2416,10 @@
         <v>648</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>14.8437</v>
+        <v>14.8482</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>140.2047</v>
+        <v>140.2371</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.015</v>
@@ -2433,10 +2433,10 @@
         <v>650</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>15.4545</v>
+        <v>15.4579</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>144.9531</v>
+        <v>144.9782</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.015</v>
@@ -2450,10 +2450,10 @@
         <v>652</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>16.0007</v>
+        <v>16.0033</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>149.4122</v>
+        <v>149.4318</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.015</v>
@@ -2467,10 +2467,10 @@
         <v>654</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>16.461</v>
+        <v>16.4629</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>153.57</v>
+        <v>153.5853</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.015</v>
@@ -2484,10 +2484,10 @@
         <v>656</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>16.8274</v>
+        <v>16.8288</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>157.6057</v>
+        <v>157.6177</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.015</v>
@@ -2501,10 +2501,10 @@
         <v>658</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>17.1708</v>
+        <v>17.1718</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>161.3788</v>
+        <v>161.388</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
@@ -2518,10 +2518,10 @@
         <v>660</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>17.4321</v>
+        <v>17.4328</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>165.1804</v>
+        <v>165.1874</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
@@ -2535,10 +2535,10 @@
         <v>662</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>17.6225</v>
+        <v>17.623</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>168.7506</v>
+        <v>168.7557</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2552,10 +2552,10 @@
         <v>664</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>17.7547</v>
+        <v>17.7551</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>172.4859</v>
+        <v>172.4892</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
@@ -2569,10 +2569,10 @@
         <v>666</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>17.8473</v>
+        <v>17.8476</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>176.0209</v>
+        <v>176.0226</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
@@ -2586,10 +2586,10 @@
         <v>668</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>17.8921</v>
+        <v>17.8924</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>179.5391</v>
+        <v>179.5393</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
@@ -2603,10 +2603,10 @@
         <v>670</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>17.8479</v>
+        <v>17.8482</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>183.1249</v>
+        <v>183.1237</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
@@ -2620,10 +2620,10 @@
         <v>672</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>17.7743</v>
+        <v>17.7747</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>186.6163</v>
+        <v>186.6136</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
@@ -2637,10 +2637,10 @@
         <v>674</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>17.641</v>
+        <v>17.6414</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>190.2069</v>
+        <v>190.2027</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
@@ -2654,10 +2654,10 @@
         <v>676</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>17.473</v>
+        <v>17.4736</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>193.6483</v>
+        <v>193.6427</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
@@ -2671,10 +2671,10 @@
         <v>678</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>17.2211</v>
+        <v>17.2219</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>197.13</v>
+        <v>197.1227</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
@@ -2688,10 +2688,10 @@
         <v>680</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>16.9349</v>
+        <v>16.936</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>200.7251</v>
+        <v>200.716</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
@@ -2705,10 +2705,10 @@
         <v>682</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>16.5913</v>
+        <v>16.5927</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>204.2726</v>
+        <v>204.2614</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
@@ -2722,10 +2722,10 @@
         <v>684</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>16.1886</v>
+        <v>16.1904</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>207.9099</v>
+        <v>207.8962</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
@@ -2739,10 +2739,10 @@
         <v>686</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>15.7481</v>
+        <v>15.7503</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>211.8218</v>
+        <v>211.8052</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
@@ -2756,10 +2756,10 @@
         <v>688</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>15.2678</v>
+        <v>15.2705</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>215.8471</v>
+        <v>215.8269</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
@@ -2773,10 +2773,10 @@
         <v>690</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>14.7463</v>
+        <v>14.7497</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>219.9395</v>
+        <v>219.915</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
@@ -2790,10 +2790,10 @@
         <v>692</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>14.1525</v>
+        <v>14.1567</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>224.4718</v>
+        <v>224.4417</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
@@ -2807,16 +2807,16 @@
         <v>694</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>13.5063</v>
+        <v>13.5114</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>229.278</v>
+        <v>229.2408</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.0728</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="140">
@@ -2824,16 +2824,16 @@
         <v>696</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>12.7621</v>
+        <v>12.7684</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>234.8076</v>
+        <v>234.7614</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.0766</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="141">
@@ -2841,16 +2841,16 @@
         <v>698</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>11.9798</v>
+        <v>11.9874</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>240.9633</v>
+        <v>240.9056</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.0814</v>
+        <v>0.0813</v>
       </c>
     </row>
     <row r="142">
@@ -2858,16 +2858,16 @@
         <v>700</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>11.0765</v>
+        <v>11.0854</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>248.1248</v>
+        <v>248.0531</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.0877</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="143">
@@ -2875,16 +2875,16 @@
         <v>702</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>10.0336</v>
+        <v>10.0437</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>256.7576</v>
+        <v>256.6695</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.0961</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="144">
@@ -2892,16 +2892,16 @@
         <v>704</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>8.9175</v>
+        <v>8.928100000000001</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>267.251</v>
+        <v>267.1457</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.1079</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="145">
@@ -2909,16 +2909,16 @@
         <v>706</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>7.6827</v>
+        <v>7.6921</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>280.709</v>
+        <v>280.5895</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1248</v>
       </c>
     </row>
     <row r="146">
@@ -2926,16 +2926,16 @@
         <v>708</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6.424</v>
+        <v>6.4296</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>298.578</v>
+        <v>298.4555</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.1492</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="147">
@@ -2943,16 +2943,16 @@
         <v>710</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>5.3135</v>
+        <v>5.3132</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>323.2983</v>
+        <v>323.204</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.179</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="148">
@@ -2960,16 +2960,16 @@
         <v>712</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>4.8051</v>
+        <v>4.8009</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>354.8714</v>
+        <v>354.8588</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.1985</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="149">
@@ -2977,10 +2977,10 @@
         <v>714</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>5.1179</v>
+        <v>5.1162</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>28.3111</v>
+        <v>28.3895</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,16 +2994,16 @@
         <v>716</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6.0416</v>
+        <v>6.0454</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>54.7488</v>
+        <v>54.8642</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.1582</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="151">
@@ -3011,16 +3011,16 @@
         <v>718</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>7.2252</v>
+        <v>7.2331</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>73.714</v>
+        <v>73.8295</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.1325</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="152">
@@ -3028,16 +3028,16 @@
         <v>720</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>8.4229</v>
+        <v>8.4323</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>87.72450000000001</v>
+        <v>87.8265</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.1139</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="153">
@@ -3045,16 +3045,16 @@
         <v>722</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>9.538</v>
+        <v>9.5472</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>98.7889</v>
+        <v>98.87390000000001</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.1011</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="154">
@@ -3062,16 +3062,16 @@
         <v>724</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>10.5336</v>
+        <v>10.5418</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>107.7445</v>
+        <v>107.8134</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.0919</v>
+        <v>0.09180000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -3079,16 +3079,16 @@
         <v>726</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>11.4009</v>
+        <v>11.4078</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>115.0736</v>
+        <v>115.1287</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.0852</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="156">
@@ -3096,16 +3096,16 @@
         <v>728</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>12.182</v>
+        <v>12.1877</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>120.9274</v>
+        <v>120.9716</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.0801</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="157">
@@ -3113,16 +3113,16 @@
         <v>730</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>12.8585</v>
+        <v>12.8632</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>126.4586</v>
+        <v>126.4939</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.0761</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="158">
@@ -3130,10 +3130,10 @@
         <v>732</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13.4693</v>
+        <v>13.4731</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>131.174</v>
+        <v>131.2024</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3147,10 +3147,10 @@
         <v>734</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>14.0417</v>
+        <v>14.0448</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>135.5011</v>
+        <v>135.5242</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
@@ -3164,16 +3164,16 @@
         <v>736</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>14.5407</v>
+        <v>14.5432</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>139.4316</v>
+        <v>139.4505</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.068</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="161">
@@ -3181,10 +3181,10 @@
         <v>738</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>14.9949</v>
+        <v>14.9969</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>143.0967</v>
+        <v>143.1122</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
@@ -3198,10 +3198,10 @@
         <v>740</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>15.4125</v>
+        <v>15.4141</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>146.4605</v>
+        <v>146.4734</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3215,10 +3215,10 @@
         <v>742</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>15.7671</v>
+        <v>15.7685</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>149.7237</v>
+        <v>149.7344</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3232,10 +3232,10 @@
         <v>744</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>16.0986</v>
+        <v>16.0997</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>152.871</v>
+        <v>152.8799</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3249,10 +3249,10 @@
         <v>746</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>16.4064</v>
+        <v>16.4072</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>156.0509</v>
+        <v>156.0583</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3266,10 +3266,10 @@
         <v>748</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>16.6606</v>
+        <v>16.6612</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>158.9506</v>
+        <v>158.9568</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
@@ -3283,10 +3283,10 @@
         <v>750</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>16.9188</v>
+        <v>16.9193</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>161.8193</v>
+        <v>161.8243</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3300,10 +3300,10 @@
         <v>752</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>17.1014</v>
+        <v>17.1018</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>164.6284</v>
+        <v>164.6325</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>754</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>17.2369</v>
+        <v>17.2373</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>167.4327</v>
+        <v>167.4359</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>756</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>17.3784</v>
+        <v>17.3786</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>170.1627</v>
+        <v>170.1652</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3351,10 +3351,10 @@
         <v>758</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>17.4581</v>
+        <v>17.4583</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>172.8946</v>
+        <v>172.8964</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3368,10 +3368,10 @@
         <v>760</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>17.5108</v>
+        <v>17.5109</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>175.5744</v>
+        <v>175.5755</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3385,10 +3385,10 @@
         <v>762</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>17.5532</v>
+        <v>17.5534</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>178.1922</v>
+        <v>178.1926</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3402,10 +3402,10 @@
         <v>764</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>17.5532</v>
+        <v>17.5533</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>180.9249</v>
+        <v>180.9247</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>766</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>17.524</v>
+        <v>17.5241</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>183.4606</v>
+        <v>183.4599</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3436,10 +3436,10 @@
         <v>768</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>17.4693</v>
+        <v>17.4695</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>186.0813</v>
+        <v>186.08</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3453,10 +3453,10 @@
         <v>770</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>17.3657</v>
+        <v>17.3659</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>188.6208</v>
+        <v>188.6189</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3470,10 +3470,10 @@
         <v>772</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>17.2482</v>
+        <v>17.2485</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>191.3706</v>
+        <v>191.368</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3487,10 +3487,10 @@
         <v>774</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>17.1235</v>
+        <v>17.1238</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>193.8164</v>
+        <v>193.8132</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3504,10 +3504,10 @@
         <v>776</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16.9233</v>
+        <v>16.9237</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>196.4521</v>
+        <v>196.4483</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3521,10 +3521,10 @@
         <v>778</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>16.7568</v>
+        <v>16.7573</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>199.0585</v>
+        <v>199.054</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3538,10 +3538,10 @@
         <v>780</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>16.5395</v>
+        <v>16.5401</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>201.9543</v>
+        <v>201.949</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3555,10 +3555,10 @@
         <v>782</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>16.2327</v>
+        <v>16.2334</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>204.602</v>
+        <v>204.5958</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3572,10 +3572,10 @@
         <v>784</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>15.9791</v>
+        <v>15.98</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>207.2817</v>
+        <v>207.2745</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3589,10 +3589,10 @@
         <v>786</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>15.668</v>
+        <v>15.669</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>210.2293</v>
+        <v>210.2211</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3606,10 +3606,10 @@
         <v>788</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>15.3581</v>
+        <v>15.3593</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>212.9505</v>
+        <v>212.9411</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3623,10 +3623,10 @@
         <v>790</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>15.0015</v>
+        <v>15.0029</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>215.9392</v>
+        <v>215.9283</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3640,10 +3640,10 @@
         <v>792</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>14.6201</v>
+        <v>14.6218</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>219.0835</v>
+        <v>219.0709</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3657,16 +3657,16 @@
         <v>794</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>14.2423</v>
+        <v>14.2442</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>222.4613</v>
+        <v>222.4467</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.0694</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="190">
@@ -3674,10 +3674,10 @@
         <v>796</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>13.7945</v>
+        <v>13.7967</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>225.8512</v>
+        <v>225.8342</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3691,10 +3691,10 @@
         <v>798</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>13.3315</v>
+        <v>13.3341</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>229.505</v>
+        <v>229.4851</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3708,10 +3708,10 @@
         <v>800</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>12.7847</v>
+        <v>12.7877</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>233.4271</v>
+        <v>233.4039</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
